--- a/data publikasi new 2.xlsx
+++ b/data publikasi new 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APLIKASI PYTHON STREAMLIT 2026\DATA PRODI S1 MATEMATIKA USU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0C157A3-5AD4-4AE1-B09D-A6D2A8026ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FFE564-395C-43FC-85A5-DE86D0AC1B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="574">
   <si>
     <t>Judul</t>
   </si>
@@ -1037,6 +1037,717 @@
   </si>
   <si>
     <t>https://www.taylorfrancis.com/chapters/edit/10.1201/9781003310792-4/semantic-information-retrieval-models-mahyuddin-nasution-elvina-herawati-marischa-elveny</t>
+  </si>
+  <si>
+    <t>A Data-Driven MINLP Approach for Enhancing Sustainability in Blockchain-Enabled e-Supply Chains</t>
+  </si>
+  <si>
+    <t>Afif Badawi; Syahril Efendi; Tulus; Herman Mawengkang</t>
+  </si>
+  <si>
+    <t>Syahril Efendi; Tulus; Herman Mawengkang</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105016543338?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://bright-journal.org/Journal/index.php/JADS/article/view/889</t>
+  </si>
+  <si>
+    <t>10.47738/jads.v6i4.889</t>
+  </si>
+  <si>
+    <t>2549-2564</t>
+  </si>
+  <si>
+    <t>Secure Data Encryption in Energy Production and Management Systems: Integrating Chaos Bifurcation and Polynomial High Order Fibonacci for Enhanced Cybersecurity</t>
+  </si>
+  <si>
+    <t>Tulus; Jonathan Liviera Marpaung; Syafrizal Sy; Kiki Ariyanti Sugeng; Rinovia Simanjuntak; Suriati</t>
+  </si>
+  <si>
+    <t>Tulus; Jonathan Liviera Marpaung; Suriati</t>
+  </si>
+  <si>
+    <t>International Journal of Safety and Security Engineering</t>
+  </si>
+  <si>
+    <t>2155-2167</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105031746420?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://iieta.org/journals/ijsse/paper/10.18280/ijsse.151018</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100785501&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.18280/ijsse.151018</t>
+  </si>
+  <si>
+    <t>An Optimization Model for Integrated Warehouse-Inventory-Transportation of a Multi-Echelon Supply Chain</t>
+  </si>
+  <si>
+    <t>Anil Hakim Syofra; Tulus; Herman Mawengkang; Muhammad Zarlis</t>
+  </si>
+  <si>
+    <t>Tulus; Herman Mawengkang; Muhammad Zarlis</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105007978755?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://etasr.com/index.php/ETASR/article/view/10932</t>
+  </si>
+  <si>
+    <t>10.48084/etasr.10932</t>
+  </si>
+  <si>
+    <t>3956-23964</t>
+  </si>
+  <si>
+    <t>Ambulance integration model in smart city for health services</t>
+  </si>
+  <si>
+    <t>Rafiqa Dewi; Tulus; Muhammad Zarlis; Erna Budhiarti Nababan</t>
+  </si>
+  <si>
+    <t>Tulus; Muhammad Zarlis; Erna Budhiarti Nababan</t>
+  </si>
+  <si>
+    <t>2264-2275</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105005275018?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://beei.org/index.php/EEI/article/view/7202</t>
+  </si>
+  <si>
+    <t>10.11591/eei.v14i3.7202</t>
+  </si>
+  <si>
+    <t>A Hybrid Decision Support Framework Using MEREC-RAFSI with Spherical Fuzzy Numbers for Selecting Banking Financial Aid Recipients</t>
+  </si>
+  <si>
+    <t>Irvanizam; Mahyuddin K. M. Nasution; Tulus; Erna Budhiarti Nababan</t>
+  </si>
+  <si>
+    <t>Mahyuddin K. M. Nasution; Tulus; Erna Budhiarti Nababan</t>
+  </si>
+  <si>
+    <t>IEEE Access</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85217558161?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10872983</t>
+  </si>
+  <si>
+    <t>33101 - 33123</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100374601&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.1109/ACCESS.2025.3539200</t>
+  </si>
+  <si>
+    <t>Analysis of MINLP-Based Reduced Gradient Method for Optimizing Coffee Plantation Maintenance Operations</t>
+  </si>
+  <si>
+    <t>Eko Hariyanto; Poltak Sihombing; Erna Budhiarti Nababan; Sawaluddin; Herman Mawengkang; Tulus</t>
+  </si>
+  <si>
+    <t>Poltak Sihombing; Erna Budhiarti Nababan; Sawaluddin; Herman Mawengkang; Tulus</t>
+  </si>
+  <si>
+    <t>2025 International Conference on Computing and Applied Informatics, ICCAI 2025</t>
+  </si>
+  <si>
+    <t>979-8-3315-7685-1</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105033592633?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/11279642</t>
+  </si>
+  <si>
+    <t>10.1109/ICCAI65301.2025.11279642</t>
+  </si>
+  <si>
+    <t>A Novel Real-Time Dynamic DEA Approach for Decision Support Under Uncertain and Evolving Operational Conditions</t>
+  </si>
+  <si>
+    <t>Jamaluddin; Syahril Efendi; Poltak Sihombing; Tulus</t>
+  </si>
+  <si>
+    <t>Syahril Efendi; Poltak Sihombing; Tulus</t>
+  </si>
+  <si>
+    <t>2025 10th International Conference on Informatics and Computing, ICIC 2025</t>
+  </si>
+  <si>
+    <t>979-8-3315-7583-0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105032116124?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/11309528</t>
+  </si>
+  <si>
+    <t>10.1109/ICIC68054.2025.11309528</t>
+  </si>
+  <si>
+    <t>Computational Analysis of Hybrid Reduced Gradient Methods for Coffee Plantation Maintenance Optimization</t>
+  </si>
+  <si>
+    <t>2025 13th International Conference on Cyber and IT Service Management, CITSM 2025</t>
+  </si>
+  <si>
+    <t>2770-159X</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105031784053?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/11291528</t>
+  </si>
+  <si>
+    <t>10.1109/CITSM67730.2025.11291528</t>
+  </si>
+  <si>
+    <t>Development of Distance Measurement Estimation Model for Specific Objects</t>
+  </si>
+  <si>
+    <t>Herdianto; Poltak Sihombing; Fahmi; Tulus</t>
+  </si>
+  <si>
+    <t>Poltak Sihombing; Tulus</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105031767114?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/11291500</t>
+  </si>
+  <si>
+    <t>10.1109/CITSM67730.2025.11291500</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT OF A DISTANCE MEASUREMENT MODEL USING A MAGNIFICATION APPROACH AND MODIFICATION OF THE YOLOV3 ARCHITECTURE</t>
+  </si>
+  <si>
+    <t>Poltak Sihombing; Fahmi; Tulus</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105027341084?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://journals.uran.ua/eejet/article/view/339774</t>
+  </si>
+  <si>
+    <t>6-15</t>
+  </si>
+  <si>
+    <t>10.15587/1729-4061.2025.339774</t>
+  </si>
+  <si>
+    <t>Analysis for Generalized of Viscoelastic Fluid with Shear-Thickening Fluids</t>
+  </si>
+  <si>
+    <t>Tulus; Mohammad Rasidi Mohammad Rasani; Md Mustafizur Rahman; Tulus Joseph Marpaung; Suriati; Yan Batara Putra Siringoringo</t>
+  </si>
+  <si>
+    <t>Tulus; Tulus Joseph Marpaung; Suriati; Yan Batara Putra Siringoringo</t>
+  </si>
+  <si>
+    <t>ICoCSETI 2025 - International Conference on Computer Sciences, Engineering, and Technology Innovation, Proceeding</t>
+  </si>
+  <si>
+    <t>979-8-3315-0861-6</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105010044484?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/11019589</t>
+  </si>
+  <si>
+    <t>10.1109/ICoCSETI63724.2025.11019589</t>
+  </si>
+  <si>
+    <t>Biomedical Simulation of Non-Newtonian Fluid Dynamics in Cardiovascular Systems: A Finite Volume Method Approach to Pulsatile Flow and Atherosclerosis Analysis</t>
+  </si>
+  <si>
+    <t>Tulus; M. R. Rasani; Md Mustafizur Rahman; Suriati; Tulus Joseph Marpaung; Yan Batara Putra Siringoringo; Jonathan Liviera Marpaung</t>
+  </si>
+  <si>
+    <t>Tulus; M. R. Rasani; Suriati; Tulus Joseph Marpaung; Yan Batara Putra Siringoringo; Jonathan Liviera Marpaung</t>
+  </si>
+  <si>
+    <t>International Journal of Energy Production and Management</t>
+  </si>
+  <si>
+    <t>275-285</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85214020325?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.acadlore.com/article/IJEPM/2024_9_4/ijepm.090408</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100903414&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.18280/ijepm.090408</t>
+  </si>
+  <si>
+    <t>R. Marpaung; Tulus; Mardiningsih</t>
+  </si>
+  <si>
+    <t>Tulus; Mardiningsih</t>
+  </si>
+  <si>
+    <t>The analysis of rock armor's resistance to sea waves using finite element</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85201228114?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/3029/1/050002/3306407/The-analysis-of-rock-armor-s-resistance-to-sea?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0192101</t>
+  </si>
+  <si>
+    <t>Hidden Markov model to provide coordination relationship for learning behavior development in the era of industrial reform</t>
+  </si>
+  <si>
+    <t>Maxtulus Junedy Nababan; Herman Mawengkang; Tulus; Sutarman</t>
+  </si>
+  <si>
+    <t>Herman Mawengkang; Tulus; Sutarman</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85201226717?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/3029/1/070004/3306425/Hidden-Markov-model-to-provide-coordination?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0198886</t>
+  </si>
+  <si>
+    <t>Computational analysis of stability of wave propagation against submerged permeable breakwater using hybrid finite element method</t>
+  </si>
+  <si>
+    <t>Tulus; Sutarman; Muhammad Romi Syahputra; Tulus Joseph Marpaung</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85201226368?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/3029/1/040022/3306401/Computational-analysis-of-stability-of-wave?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0192099</t>
+  </si>
+  <si>
+    <t>Computational analysis of stability of wave propagation against submerged permeable breakwater using boundary element method</t>
+  </si>
+  <si>
+    <t>Jonathan Liviera Marpaung; Tulus; Parapat Gultom</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85201196399?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/3029/1/040011/3306390/Computational-analysis-of-stability-of-wave?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0192100</t>
+  </si>
+  <si>
+    <t>Mathematical Study Simulating Hydroelectric Power as a Renewable Green Energy Alternative</t>
+  </si>
+  <si>
+    <t>Tulus; Semin; Muhammad Romi Syahputra; Tulus Joseph Marpaung; Jonathan Liviera Marpaung</t>
+  </si>
+  <si>
+    <t>Tulus; Muhammad Romi Syahputra; Tulus Joseph Marpaung; Jonathan Liviera Marpaung</t>
+  </si>
+  <si>
+    <t>Mathematical Modelling of Engineering Problems</t>
+  </si>
+  <si>
+    <t>1877-1884</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85200409000?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://iieta.org/journals/mmep/paper/10.18280/mmep.110717</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100863633&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.18280/mmep.110717</t>
+  </si>
+  <si>
+    <t>Improving data security with the utilization of matrix columnar transposition techniques</t>
+  </si>
+  <si>
+    <t>Tulus; Syafrizal Sy; Kiki A. Sugeng; Rinovia Simanjuntak; Jonathan Liviera Marpaung</t>
+  </si>
+  <si>
+    <t>Tulus; Jonathan Liviera Marpaung</t>
+  </si>
+  <si>
+    <t>E3S Web of Conferences</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85189242893?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.e3s-conferences.org/articles/e3sconf/abs/2024/31/e3sconf_iccsei2023_02004/e3sconf_iccsei2023_02004.html</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100795900&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.1051/e3sconf/202450102004</t>
+  </si>
+  <si>
+    <t>Area Recognition Based on Grid Structure for Rice Paddy Monitoring Using Wireless Sensor Network</t>
+  </si>
+  <si>
+    <t>Bambang Haryanto Marpaung; Benny Benyamin Nasution; Tulus</t>
+  </si>
+  <si>
+    <t>Tulus</t>
+  </si>
+  <si>
+    <t>2024 8th International Conference on Information Technology, Information Systems and Electrical Engineering, ICITISEE 2024</t>
+  </si>
+  <si>
+    <t>979-8-3503-6897-0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85210487206?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10730174</t>
+  </si>
+  <si>
+    <t>10.1109/ICITISEE63424.2024.10730174</t>
+  </si>
+  <si>
+    <t>Distance antimagic labeling of circulant graphs</t>
+  </si>
+  <si>
+    <t>Syafrizal Sy; Rinovia Simanjuntak; Tamaro Nadeak; Kiki Ariyanti Sugeng; Tulus</t>
+  </si>
+  <si>
+    <t>AIMS Mathematics</t>
+  </si>
+  <si>
+    <t>21177-21188</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85197288921?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.aimspress.com/article/doi/10.3934/math.20241028</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100927407&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.3934/math.20241028</t>
+  </si>
+  <si>
+    <t>Optimization Model for Outpatient Services Capacity Management in Different Patient Conditions and Diseases</t>
+  </si>
+  <si>
+    <t>Poningsih; Poltak Sihombing; Muhammad Zarlis; Tulus</t>
+  </si>
+  <si>
+    <t>Poltak Sihombing; Muhammad Zarlis; Tulus</t>
+  </si>
+  <si>
+    <t>IAENG International Journal of Computer Science</t>
+  </si>
+  <si>
+    <t>1819656X</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85189474788?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.iaeng.org/IJCS/issues_v51/issue_3/IJCS_51_3_11.pdf</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=15900154752&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>260-266</t>
+  </si>
+  <si>
+    <t>An Extended CRITIC Algorithm Based on Spherical Fuzzy Sets to Determine the Objective Weights of Decision-Makers</t>
+  </si>
+  <si>
+    <t>Irvanizam Irvanizam; Mahyuddin K. M. Nasution; Tulus; Erna Budhiarti Nababan</t>
+  </si>
+  <si>
+    <t>2024 9th International Conference on Informatics and Computing, ICIC 2024</t>
+  </si>
+  <si>
+    <t>979-8-3315-1760-1</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105004579764?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10956362</t>
+  </si>
+  <si>
+    <t>10.1109/ICIC64337.2024.10956362</t>
+  </si>
+  <si>
+    <t>Improving Object Distance Measurement Based on Mono Camera Using Magnification and Yolo Methods</t>
+  </si>
+  <si>
+    <t>International Conference on Control and Automation, Electronics, Robotics, Internet of Things, and Artificial Intelligence, CERIA 2024</t>
+  </si>
+  <si>
+    <t>979-8-3315-1116-6</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105001568590?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10914711</t>
+  </si>
+  <si>
+    <t>10.1109/CERIA64726.2024.10914711</t>
+  </si>
+  <si>
+    <t>Computational Assessment of Wave Stability Against Submerged Permeable Breakwaters: A Hybrid Finite Element Method Approach</t>
+  </si>
+  <si>
+    <t>Tulus; Md Mustafizur Rahman; Sutarman; Muhammad Romi Syahputra; Tulus Joseph Marpaung; Jonathan Liviera Marpaung</t>
+  </si>
+  <si>
+    <t>Tulus; Sutarman; Muhammad Romi Syahputra; Tulus Joseph Marpaung; Jonathan Liviera Marpaung</t>
+  </si>
+  <si>
+    <t>1977-1986</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85184191976?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://iieta.org/journals/mmep/paper/10.18280/mmep.100607</t>
+  </si>
+  <si>
+    <t>10.18280/mmep.100607</t>
+  </si>
+  <si>
+    <t>A framework of nonparametric regression to predict natural gas demand</t>
+  </si>
+  <si>
+    <t>Rani F. Sinaga; Sutarman; Tulus; Open Darnius; Herman Mawengkang</t>
+  </si>
+  <si>
+    <t>Sutarman; Tulus; Open Darnius; Herman Mawengkang</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85160275211?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/2714/1/030041/2889712/A-framework-of-nonparametric-regression-to-predict?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0128460</t>
+  </si>
+  <si>
+    <t>Heat transfer in non-Newtonian fluid</t>
+  </si>
+  <si>
+    <t>Sarah Violita Sirait; Tulus; Mardiningsih</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85160265317?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/2714/1/020056/2889745/Heat-transfer-in-non-Newtonian-fluid?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0133901</t>
+  </si>
+  <si>
+    <t>Optimization Model of Integrated Sustainable Forest Management Planning for Hydropower Power Plant</t>
+  </si>
+  <si>
+    <t>J. A. Br Sinaga; Mahyuddin K. M. Nasution; Herman Mawengkang; Tulus</t>
+  </si>
+  <si>
+    <t>Mahyuddin K. M. Nasution; Herman Mawengkang; Tulus</t>
+  </si>
+  <si>
+    <t>2001-2011</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85163897107?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.naturalspublishing.com/Article.asp?ArtcID=27003</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100970313&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.18576/isl/120540</t>
+  </si>
+  <si>
+    <t>Use of Yellow Sticky Trap (YST) and coffee experts (pakar kopi) reduces coffee pest attacks in Perteguhan Hamlet, Telagah Villages, Langkat District, North Sumatra</t>
+  </si>
+  <si>
+    <t>A Z Siregar; Tulus</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85176103430?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/article/10.1088/1755-1315/1241/1/012111</t>
+  </si>
+  <si>
+    <t>10.1088/1755-1315/1241/1/012111</t>
+  </si>
+  <si>
+    <t>Computational analysis dynamics fluid of flow in dam using COMSOL Multiphysics</t>
+  </si>
+  <si>
+    <t>Masna; Tulus; Sawal</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85147325946?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/article/10.1088/1742-6596/2421/1/012047</t>
+  </si>
+  <si>
+    <t>10.1088/1742-6596/2421/1/012047</t>
+  </si>
+  <si>
+    <t>Computational Analysis for Dam Stability Against Water Flow Pressure</t>
+  </si>
+  <si>
+    <t>Tulus; Tulus Joseph Marpaung; Jonathan Liviera Marpaung</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85147324854?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/article/10.1088/1742-6596/2421/1/012013</t>
+  </si>
+  <si>
+    <t>10.1088/1742-6596/2421/1/012013</t>
+  </si>
+  <si>
+    <t>The Use of Biopesticide to Control of Thrips palmi on potato Plant of Sorik Merapi Mountain, Madina, North Sumatera</t>
+  </si>
+  <si>
+    <t>A Z Siregar; Tulus; Yunilas; S C A Nisa</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85128788647?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/article/10.1088/1755-1315/1005/1/012019</t>
+  </si>
+  <si>
+    <t>10.1088/1755-1315/1005/1/012019</t>
+  </si>
+  <si>
+    <t>Integrating Ambulance into GIS in Smart City: Problems and Prospect with P-Median Model</t>
+  </si>
+  <si>
+    <t>2022 4th International Conference on Cybernetics and Intelligent System, ICORIS 2022</t>
+  </si>
+  <si>
+    <t>10.1109/ICORIS56080.2022.10031390</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85148487784?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10031390</t>
+  </si>
+  <si>
+    <t>978-1-6654-5395-0</t>
+  </si>
+  <si>
+    <t>Inventory insects of sorghum plantation in Northern Sumatera, Indonesia</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85135153321?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/article/10.1088/1755-1315/977/1/012105</t>
+  </si>
+  <si>
+    <t>10.1088/1755-1315/977/1/012105</t>
+  </si>
+  <si>
+    <t>Adaboost Hybrid Algorithm with Color Space Transformation and Lighting Compensation Method to Detect Face Based on Emotion</t>
+  </si>
+  <si>
+    <t>Ade Linhar P; Tulus; Muhammad Zarlis</t>
+  </si>
+  <si>
+    <t>Tulus; Muhammad Zarlis</t>
+  </si>
+  <si>
+    <t>InHeNce 2021 - 2021 IEEE International Conference on Health, Instrumentation and Measurement, and Natural Sciences</t>
+  </si>
+  <si>
+    <t>978-1-6654-4181-0</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85115918720?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/9537257</t>
+  </si>
+  <si>
+    <t>10.1109/InHeNce52833.2021.9537257</t>
+  </si>
+  <si>
+    <t>Optimization and Computing Model of Fish Resource Supply Chain Distribution Network</t>
+  </si>
+  <si>
+    <t>Nurdin; Muhammad Zarlis, Tulus; Syahril Efendi</t>
+  </si>
+  <si>
+    <t>Muhammad Zarlis, Tulus; Syahril Efendi</t>
+  </si>
+  <si>
+    <t>10.1088/1742-6596/1898/1/012022</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85108996410?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/article/10.1088/1742-6596/1898/1/012022</t>
   </si>
 </sst>
 </file>
@@ -1373,7 +2084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="67.5703125" style="1" customWidth="1"/>
@@ -3408,6 +4119,1564 @@
         <v>3</v>
       </c>
       <c r="R45" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" s="1">
+        <v>27236471</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H46" s="1">
+        <v>6</v>
+      </c>
+      <c r="I46" s="1">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="P46" s="1">
+        <v>1</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="F47" s="1">
+        <v>20419031</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H47" s="1">
+        <v>15</v>
+      </c>
+      <c r="I47" s="1">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="R47" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" s="1">
+        <v>17928036</v>
+      </c>
+      <c r="G48" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H48" s="1">
+        <v>15</v>
+      </c>
+      <c r="I48" s="1">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="R48" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F49" s="1">
+        <v>20893191</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H49" s="1">
+        <v>14</v>
+      </c>
+      <c r="I49" s="1">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="R49" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="F50" s="1">
+        <v>21693536</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H50" s="1">
+        <v>13</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="P50" s="1">
+        <v>11</v>
+      </c>
+      <c r="R50" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="R51" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G54" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F55" s="1">
+        <v>17293774</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H55" s="1">
+        <v>6</v>
+      </c>
+      <c r="I55" s="1">
+        <v>9</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="R55" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="G56" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F57" s="1">
+        <v>20563272</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H57" s="1">
+        <v>9</v>
+      </c>
+      <c r="I57" s="1">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="P57" s="1">
+        <v>4</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H58" s="1">
+        <v>3029</v>
+      </c>
+      <c r="I58" s="1">
+        <v>1</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="R58" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G59" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H59" s="1">
+        <v>3029</v>
+      </c>
+      <c r="I59" s="1">
+        <v>1</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="R59" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G60" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H60" s="1">
+        <v>3029</v>
+      </c>
+      <c r="I60" s="1">
+        <v>1</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="P60" s="1">
+        <v>5</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G61" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H61" s="1">
+        <v>3029</v>
+      </c>
+      <c r="I61" s="1">
+        <v>1</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="R61" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F62" s="1">
+        <v>23690739</v>
+      </c>
+      <c r="G62" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H62" s="1">
+        <v>11</v>
+      </c>
+      <c r="I62" s="1">
+        <v>7</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="P62" s="1">
+        <v>7</v>
+      </c>
+      <c r="R62" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="F63" s="1">
+        <v>22671242</v>
+      </c>
+      <c r="G63" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H63" s="1">
+        <v>501</v>
+      </c>
+      <c r="I63" s="1">
+        <v>1</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="P63" s="1">
+        <v>11</v>
+      </c>
+      <c r="R63" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="R64" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="F65" s="1">
+        <v>24736988</v>
+      </c>
+      <c r="G65" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H65" s="1">
+        <v>9</v>
+      </c>
+      <c r="I65" s="1">
+        <v>8</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="P65" s="1">
+        <v>2</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="G66" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H66" s="1">
+        <v>51</v>
+      </c>
+      <c r="I66" s="1">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="P66" s="1">
+        <v>3</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="G67" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="P67" s="1">
+        <v>6</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="P68" s="1">
+        <v>3</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F69" s="1">
+        <v>23690739</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H69" s="1">
+        <v>10</v>
+      </c>
+      <c r="I69" s="1">
+        <v>6</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="P69" s="1">
+        <v>11</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H70" s="1">
+        <v>2714</v>
+      </c>
+      <c r="I70" s="1">
+        <v>1</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G71" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H71" s="1">
+        <v>2714</v>
+      </c>
+      <c r="I71" s="1">
+        <v>1</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F72" s="1">
+        <v>20909551</v>
+      </c>
+      <c r="G72" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H72" s="1">
+        <v>12</v>
+      </c>
+      <c r="I72" s="1">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="P72" s="1">
+        <v>1</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F73" s="1">
+        <v>17551307</v>
+      </c>
+      <c r="G73" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H73" s="1">
+        <v>1241</v>
+      </c>
+      <c r="I73" s="1">
+        <v>1</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="P73" s="1">
+        <v>1</v>
+      </c>
+      <c r="R73" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F74" s="1">
+        <v>17426588</v>
+      </c>
+      <c r="G74" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H74" s="1">
+        <v>2421</v>
+      </c>
+      <c r="I74" s="1">
+        <v>1</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="P74" s="1">
+        <v>1</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F75" s="1">
+        <v>17426588</v>
+      </c>
+      <c r="G75" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H75" s="1">
+        <v>2421</v>
+      </c>
+      <c r="I75" s="1">
+        <v>1</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="P75" s="1">
+        <v>10</v>
+      </c>
+      <c r="R75" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F76" s="1">
+        <v>17551307</v>
+      </c>
+      <c r="G76" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H76" s="1">
+        <v>1005</v>
+      </c>
+      <c r="I76" s="1">
+        <v>1</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="P76" s="1">
+        <v>1</v>
+      </c>
+      <c r="R76" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="G77" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="P77" s="1">
+        <v>1</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F78" s="1">
+        <v>17551307</v>
+      </c>
+      <c r="G78" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H78" s="1">
+        <v>977</v>
+      </c>
+      <c r="I78" s="1">
+        <v>1</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="P78" s="1">
+        <v>1</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="G79" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="R79" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F80" s="1">
+        <v>17426588</v>
+      </c>
+      <c r="G80" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H80" s="1">
+        <v>1989</v>
+      </c>
+      <c r="I80" s="1">
+        <v>1</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="P80" s="1">
+        <v>4</v>
+      </c>
+      <c r="R80" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3540,6 +5809,100 @@
     <hyperlink ref="N44" r:id="rId125" xr:uid="{2601B3E4-C3D3-472A-BCA1-F16A4684E5CB}"/>
     <hyperlink ref="K45" r:id="rId126" xr:uid="{62D9F48F-400F-418C-9733-C56FE95796F5}"/>
     <hyperlink ref="L45" r:id="rId127" xr:uid="{A46EDA6E-59E3-4B4B-ABA8-BFE2A25AF1DF}"/>
+    <hyperlink ref="K46" r:id="rId128" xr:uid="{54D9FC16-0DF5-453B-B590-FA8A56BC5EC4}"/>
+    <hyperlink ref="L46" r:id="rId129" xr:uid="{F509952C-DC18-48C1-8E9D-272E31A62274}"/>
+    <hyperlink ref="N46" r:id="rId130" xr:uid="{61E01760-DA8D-442F-B27D-D9233C381156}"/>
+    <hyperlink ref="K47" r:id="rId131" xr:uid="{87DD20F0-0C4E-42BB-951A-207A050D7D65}"/>
+    <hyperlink ref="L47" r:id="rId132" xr:uid="{15C98EEA-FA87-47E4-911E-694F8980847F}"/>
+    <hyperlink ref="N47" r:id="rId133" xr:uid="{09BD01AD-C093-49C2-857B-D66541885535}"/>
+    <hyperlink ref="K48" r:id="rId134" xr:uid="{ACDE17B2-327D-4F7A-B003-F7BAA1F684F9}"/>
+    <hyperlink ref="L48" r:id="rId135" xr:uid="{C02DDB00-2295-4B2A-9A4F-694588B9209F}"/>
+    <hyperlink ref="N48" r:id="rId136" xr:uid="{622F01ED-6BF7-48AF-AEB0-725237677B06}"/>
+    <hyperlink ref="K49" r:id="rId137" xr:uid="{E7AD2CFE-A841-44BA-A5D5-4340E93C1540}"/>
+    <hyperlink ref="L49" r:id="rId138" xr:uid="{006711AB-E89B-4A25-B585-377CA4C9E884}"/>
+    <hyperlink ref="N49" r:id="rId139" xr:uid="{F1BCDA95-33EB-4043-9281-BEC6877AC938}"/>
+    <hyperlink ref="K50" r:id="rId140" xr:uid="{5C89B48D-B5C3-42D7-9C88-B2D889ED0D08}"/>
+    <hyperlink ref="L50" r:id="rId141" xr:uid="{7A75C0ED-B335-4358-9ED4-591FCF3AD52C}"/>
+    <hyperlink ref="N50" r:id="rId142" xr:uid="{157C6AA0-0734-4EBD-AE93-BFC9E047CFB5}"/>
+    <hyperlink ref="K51" r:id="rId143" xr:uid="{A28B8BDE-394D-4AFF-9464-8F1C87B40F8F}"/>
+    <hyperlink ref="L51" r:id="rId144" xr:uid="{BE4CB19F-72CD-4F54-9FA2-13A5FA6E0DB7}"/>
+    <hyperlink ref="K52" r:id="rId145" xr:uid="{AB5FA37E-6867-462B-BA38-2920BF87A2FF}"/>
+    <hyperlink ref="L52" r:id="rId146" xr:uid="{30E73CEC-299E-4BF4-BBD0-73025A92B012}"/>
+    <hyperlink ref="K53" r:id="rId147" xr:uid="{3D62C608-A95D-47C0-A694-0341CB347666}"/>
+    <hyperlink ref="L53" r:id="rId148" xr:uid="{38D3E984-EE0D-4D11-AE5A-058EDC9A2D77}"/>
+    <hyperlink ref="K54" r:id="rId149" xr:uid="{3B0C8339-D2FB-4ED1-BC72-65F9E9E05549}"/>
+    <hyperlink ref="L54" r:id="rId150" xr:uid="{D5A05FF4-1DEA-4480-826A-BEDC4FFFED75}"/>
+    <hyperlink ref="K55" r:id="rId151" xr:uid="{8BB73353-42D8-430A-98FD-0AEF27208D40}"/>
+    <hyperlink ref="L55" r:id="rId152" xr:uid="{B2EE306A-E319-4011-8A6C-6AA8BD5AABDD}"/>
+    <hyperlink ref="N55" r:id="rId153" xr:uid="{F086A51C-5E23-46CD-BF96-BB3B3510EFFC}"/>
+    <hyperlink ref="K56" r:id="rId154" xr:uid="{67E052CA-DF59-4A9B-B2FA-EC77FBCCD389}"/>
+    <hyperlink ref="L56" r:id="rId155" xr:uid="{F4FC0E32-4F0E-4847-A5B5-807331F807E3}"/>
+    <hyperlink ref="K57" r:id="rId156" xr:uid="{059F9660-C731-4F3D-A179-8BD262FA0A2D}"/>
+    <hyperlink ref="L57" r:id="rId157" xr:uid="{4917D263-8743-4B29-A5D6-3972786A7B45}"/>
+    <hyperlink ref="N57" r:id="rId158" xr:uid="{E05B5683-2AE5-4524-9817-675A0E7F25BA}"/>
+    <hyperlink ref="K58" r:id="rId159" xr:uid="{E3916402-0923-44A3-BCBA-E5D547A2A209}"/>
+    <hyperlink ref="L58" r:id="rId160" xr:uid="{2A3695FB-9EA6-489F-920C-E44A0DBD7303}"/>
+    <hyperlink ref="N58" r:id="rId161" xr:uid="{06C68413-13A3-49C8-9B61-F88460F87115}"/>
+    <hyperlink ref="K59" r:id="rId162" xr:uid="{4192416C-7954-432B-9993-D6ABABDC8F52}"/>
+    <hyperlink ref="L59" r:id="rId163" xr:uid="{B794BB0B-E54B-430C-A734-2E8E01D6E968}"/>
+    <hyperlink ref="N59" r:id="rId164" xr:uid="{D8C29CD6-2AAF-4182-86BD-C173DB300916}"/>
+    <hyperlink ref="K60" r:id="rId165" xr:uid="{43EED1D3-54A0-4AE9-800A-0653C2BCC08F}"/>
+    <hyperlink ref="L60" r:id="rId166" xr:uid="{90C67610-5567-4FFA-9DE5-F116373CC359}"/>
+    <hyperlink ref="N60" r:id="rId167" xr:uid="{FAF4B470-0A0C-418E-894B-C0E33315AB88}"/>
+    <hyperlink ref="K61" r:id="rId168" xr:uid="{37F16E29-6C19-4A5C-B007-7A62FA8CFEBC}"/>
+    <hyperlink ref="L61" r:id="rId169" xr:uid="{000742B8-3526-466B-88C1-C6760B271833}"/>
+    <hyperlink ref="N61" r:id="rId170" xr:uid="{614EB07A-7E2F-4D2C-959A-976B9F456BB9}"/>
+    <hyperlink ref="K62" r:id="rId171" xr:uid="{F0E30FA9-350E-4DFD-84C7-CF782124D8F1}"/>
+    <hyperlink ref="L62" r:id="rId172" xr:uid="{95C35B3A-1BC3-4A33-B4B7-4580B820395C}"/>
+    <hyperlink ref="N62" r:id="rId173" xr:uid="{95A0925D-8C00-4320-9CA4-9A2D8A95FA28}"/>
+    <hyperlink ref="K63" r:id="rId174" xr:uid="{ED729E87-0304-4C75-A923-B70A0A9838B4}"/>
+    <hyperlink ref="L63" r:id="rId175" xr:uid="{E25E4815-68CB-40D0-8BB5-D74476FDA29A}"/>
+    <hyperlink ref="N63" r:id="rId176" xr:uid="{E40A5E61-73A9-4A77-94B2-88F178F36536}"/>
+    <hyperlink ref="K64" r:id="rId177" xr:uid="{6FD1A203-40DE-4B17-A7AB-DA26DA5B4F2E}"/>
+    <hyperlink ref="L64" r:id="rId178" xr:uid="{1EA19264-D5C8-40C7-B2AA-9064595B1430}"/>
+    <hyperlink ref="K65" r:id="rId179" xr:uid="{176452B8-5839-493D-AB21-7C345A0A7C53}"/>
+    <hyperlink ref="L65" r:id="rId180" xr:uid="{37D24190-BC1F-4256-971D-2822D447E2C0}"/>
+    <hyperlink ref="N65" r:id="rId181" xr:uid="{BB618418-39BD-4ABB-8F14-9E60DF82B0E2}"/>
+    <hyperlink ref="K66" r:id="rId182" xr:uid="{7BA47420-6ED9-41ED-B98F-3341310E8212}"/>
+    <hyperlink ref="L66" r:id="rId183" xr:uid="{33DFC853-985A-4675-9D4A-03250D129A77}"/>
+    <hyperlink ref="N66" r:id="rId184" xr:uid="{37EBF0B5-50E8-40DA-B444-F725105931AE}"/>
+    <hyperlink ref="K67" r:id="rId185" xr:uid="{4A514006-8609-4A14-A066-AF18E34B12F9}"/>
+    <hyperlink ref="L67" r:id="rId186" xr:uid="{47A05059-EBD8-47EB-8480-CCFF794D8887}"/>
+    <hyperlink ref="K68" r:id="rId187" xr:uid="{4AE6FDE0-882A-4151-984B-8E80F1E06421}"/>
+    <hyperlink ref="L68" r:id="rId188" xr:uid="{B5C162C0-6E82-4E17-823A-596A5D41A3B3}"/>
+    <hyperlink ref="K69" r:id="rId189" xr:uid="{005DFC50-AF96-4F8E-A546-50A6DBC0ADF0}"/>
+    <hyperlink ref="L69" r:id="rId190" xr:uid="{91173319-48EA-4ECE-86C9-A1662F2EF1DE}"/>
+    <hyperlink ref="N69" r:id="rId191" xr:uid="{86BDAF96-6C90-42BB-846A-6F2CBFD2600A}"/>
+    <hyperlink ref="K70" r:id="rId192" xr:uid="{7F01EAE4-CDBC-4F5E-9447-4713A40885E9}"/>
+    <hyperlink ref="L70" r:id="rId193" xr:uid="{047B7977-B381-44C8-A858-555550CF16FB}"/>
+    <hyperlink ref="N70" r:id="rId194" xr:uid="{FFD723D0-DDE7-4A41-A9A0-217E724271CF}"/>
+    <hyperlink ref="K71" r:id="rId195" xr:uid="{01310167-08C1-452C-8115-E4E7488A7C2A}"/>
+    <hyperlink ref="L71" r:id="rId196" xr:uid="{3645B27F-28AB-457C-8D1D-FE3F79F7733C}"/>
+    <hyperlink ref="N71" r:id="rId197" xr:uid="{C00195B0-911F-4A78-952A-73EC21D8FF24}"/>
+    <hyperlink ref="K72" r:id="rId198" xr:uid="{8E7153AF-9E22-4B0E-94CA-DA3227E4D2B3}"/>
+    <hyperlink ref="L72" r:id="rId199" xr:uid="{C87BFEAD-85BC-4186-AFDA-4E1C07FFC8BF}"/>
+    <hyperlink ref="N72" r:id="rId200" xr:uid="{6FB42101-0065-4697-BD1B-113F104A0DE5}"/>
+    <hyperlink ref="N73" r:id="rId201" xr:uid="{0C16A11F-C1D8-4EF6-A5F4-ACF5B1A1DAEC}"/>
+    <hyperlink ref="K73" r:id="rId202" xr:uid="{21DE0B2F-F4B3-492B-86FB-011EC6363235}"/>
+    <hyperlink ref="L73" r:id="rId203" xr:uid="{04330E41-9FD5-4782-B236-D330D5D07C3A}"/>
+    <hyperlink ref="N74" r:id="rId204" xr:uid="{ABD41A5C-84B2-4AA6-A1A0-57C78A3DCC11}"/>
+    <hyperlink ref="K74" r:id="rId205" xr:uid="{20F6D8D9-7228-44AB-9B29-FC22FE951C9E}"/>
+    <hyperlink ref="L74" r:id="rId206" xr:uid="{7135F869-D8A1-4229-B0AA-4158FC90F897}"/>
+    <hyperlink ref="K75" r:id="rId207" xr:uid="{95D355BE-ED50-47D4-A8CA-3A5786766081}"/>
+    <hyperlink ref="L75" r:id="rId208" xr:uid="{7F4C3587-5468-48BD-8E1C-C9F9A66AA116}"/>
+    <hyperlink ref="N75" r:id="rId209" xr:uid="{2B35FFC0-D6A2-46D9-AEF9-4959E77B3F99}"/>
+    <hyperlink ref="N76" r:id="rId210" xr:uid="{6D6C2655-B9D1-4B0F-9969-B706F72340B3}"/>
+    <hyperlink ref="K76" r:id="rId211" xr:uid="{268B929C-8713-4FF6-8349-4FDE25C7E3A1}"/>
+    <hyperlink ref="L76" r:id="rId212" xr:uid="{E2287AC7-36B3-4941-84BC-E8B46820F854}"/>
+    <hyperlink ref="K77" r:id="rId213" xr:uid="{BE1D3BF0-B479-45B5-BCF2-A94E62964CCC}"/>
+    <hyperlink ref="L77" r:id="rId214" xr:uid="{8A4864CE-3C83-40E9-A1C4-455042C4FB1E}"/>
+    <hyperlink ref="K78" r:id="rId215" xr:uid="{88C72EA0-7263-4638-8F00-59C8F8B9A0EB}"/>
+    <hyperlink ref="L78" r:id="rId216" xr:uid="{DBDC0BAC-4D1A-43EA-8778-8B5273CE2A20}"/>
+    <hyperlink ref="K79" r:id="rId217" xr:uid="{751BCB4C-A344-4921-BF41-7B1BBC075EBD}"/>
+    <hyperlink ref="L79" r:id="rId218" xr:uid="{879E0155-4A8E-4248-9390-12681D8834B3}"/>
+    <hyperlink ref="K80" r:id="rId219" xr:uid="{9131CD4B-AE06-4699-8407-9AB381F58ECC}"/>
+    <hyperlink ref="L80" r:id="rId220" xr:uid="{08E5EC40-1D1E-4B6C-9AE4-874B900E29B7}"/>
+    <hyperlink ref="N80" r:id="rId221" xr:uid="{028F3432-7648-4C56-AD5E-005B4F1AE037}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
